--- a/design/tables/Obstacle.xlsx
+++ b/design/tables/Obstacle.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Obstacle" sheetId="1" r:id="R26e2c067df684bad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Obstacle" sheetId="1" r:id="R6a5e984dd65141ea"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -4388,6 +4388,206 @@
         <x:v>57</x:v>
       </x:c>
     </x:row>
+    <x:row r="206">
+      <x:c r="A206" t="n">
+        <x:v>2011</x:v>
+      </x:c>
+      <x:c r="B206" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C206" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D206" t="str">
+        <x:v>plant</x:v>
+      </x:c>
+      <x:c r="E206" t="n">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="F206" t="n">
+        <x:v>48</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="207">
+      <x:c r="A207" t="n">
+        <x:v>2012</x:v>
+      </x:c>
+      <x:c r="B207" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C207" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D207" t="str">
+        <x:v>crate</x:v>
+      </x:c>
+      <x:c r="E207" t="n">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="F207" t="n">
+        <x:v>62</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="208">
+      <x:c r="A208" t="n">
+        <x:v>2013</x:v>
+      </x:c>
+      <x:c r="B208" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C208" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D208" t="str">
+        <x:v>basket</x:v>
+      </x:c>
+      <x:c r="E208" t="n">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="F208" t="n">
+        <x:v>46</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="209">
+      <x:c r="A209" t="n">
+        <x:v>2014</x:v>
+      </x:c>
+      <x:c r="B209" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C209" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D209" t="str">
+        <x:v>crate</x:v>
+      </x:c>
+      <x:c r="E209" t="n">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="F209" t="n">
+        <x:v>68</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="210">
+      <x:c r="A210" t="n">
+        <x:v>2015</x:v>
+      </x:c>
+      <x:c r="B210" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C210" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="D210" t="str">
+        <x:v>plant</x:v>
+      </x:c>
+      <x:c r="E210" t="n">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="F210" t="n">
+        <x:v>52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="211">
+      <x:c r="A211" t="n">
+        <x:v>2016</x:v>
+      </x:c>
+      <x:c r="B211" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C211" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D211" t="str">
+        <x:v>basket</x:v>
+      </x:c>
+      <x:c r="E211" t="n">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="F211" t="n">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="212">
+      <x:c r="A212" t="n">
+        <x:v>2017</x:v>
+      </x:c>
+      <x:c r="B212" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C212" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D212" t="str">
+        <x:v>crate</x:v>
+      </x:c>
+      <x:c r="E212" t="n">
+        <x:v>236</x:v>
+      </x:c>
+      <x:c r="F212" t="n">
+        <x:v>70</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="213">
+      <x:c r="A213" t="n">
+        <x:v>2018</x:v>
+      </x:c>
+      <x:c r="B213" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C213" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D213" t="str">
+        <x:v>plant</x:v>
+      </x:c>
+      <x:c r="E213" t="n">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="F213" t="n">
+        <x:v>54</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="214">
+      <x:c r="A214" t="n">
+        <x:v>2019</x:v>
+      </x:c>
+      <x:c r="B214" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C214" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="D214" t="str">
+        <x:v>basket</x:v>
+      </x:c>
+      <x:c r="E214" t="n">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="F214" t="n">
+        <x:v>54</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="215">
+      <x:c r="A215" t="n">
+        <x:v>2020</x:v>
+      </x:c>
+      <x:c r="B215" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C215" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D215" t="str">
+        <x:v>crate</x:v>
+      </x:c>
+      <x:c r="E215" t="n">
+        <x:v>248</x:v>
+      </x:c>
+      <x:c r="F215" t="n">
+        <x:v>74</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/design/tables/Obstacle.xlsx
+++ b/design/tables/Obstacle.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Obstacle" sheetId="1" r:id="R6a5e984dd65141ea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Obstacle" sheetId="1" r:id="Rb4e0de51a8e6494e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -3970,579 +3970,579 @@
     </x:row>
     <x:row r="185" ht="15" hidden="0" customHeight="1">
       <x:c r="A185" s="7" t="n">
-        <x:v>1810</x:v>
+        <x:v>1901</x:v>
       </x:c>
       <x:c r="B185" s="7" t="n">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C185" s="7" t="n">
-        <x:v>20</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D185" s="2" t="str">
         <x:v>basket</x:v>
       </x:c>
       <x:c r="E185" s="7" t="n">
-        <x:v>217</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="F185" s="7" t="n">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="186" ht="15" hidden="0" customHeight="1">
       <x:c r="A186" s="7" t="n">
-        <x:v>1901</x:v>
+        <x:v>1902</x:v>
       </x:c>
       <x:c r="B186" s="7" t="n">
         <x:v>19</x:v>
       </x:c>
       <x:c r="C186" s="7" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D186" s="2" t="str">
-        <x:v>basket</x:v>
+        <x:v>crate</x:v>
       </x:c>
       <x:c r="E186" s="7" t="n">
-        <x:v>178</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="F186" s="7" t="n">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="187" ht="15" hidden="0" customHeight="1">
       <x:c r="A187" s="7" t="n">
-        <x:v>1902</x:v>
+        <x:v>1903</x:v>
       </x:c>
       <x:c r="B187" s="7" t="n">
         <x:v>19</x:v>
       </x:c>
       <x:c r="C187" s="7" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D187" s="2" t="str">
-        <x:v>crate</x:v>
+        <x:v>plant</x:v>
       </x:c>
       <x:c r="E187" s="7" t="n">
-        <x:v>183</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="F187" s="7" t="n">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="188" ht="15" hidden="0" customHeight="1">
       <x:c r="A188" s="7" t="n">
-        <x:v>1903</x:v>
+        <x:v>1904</x:v>
       </x:c>
       <x:c r="B188" s="7" t="n">
         <x:v>19</x:v>
       </x:c>
       <x:c r="C188" s="7" t="n">
-        <x:v>5</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D188" s="2" t="str">
-        <x:v>plant</x:v>
+        <x:v>basket</x:v>
       </x:c>
       <x:c r="E188" s="7" t="n">
-        <x:v>188</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="F188" s="7" t="n">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="189" ht="15" hidden="0" customHeight="1">
       <x:c r="A189" s="7" t="n">
-        <x:v>1904</x:v>
+        <x:v>1905</x:v>
       </x:c>
       <x:c r="B189" s="7" t="n">
         <x:v>19</x:v>
       </x:c>
       <x:c r="C189" s="7" t="n">
-        <x:v>7</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D189" s="2" t="str">
-        <x:v>basket</x:v>
+        <x:v>crate</x:v>
       </x:c>
       <x:c r="E189" s="7" t="n">
-        <x:v>193</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="F189" s="7" t="n">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="190" ht="15" hidden="0" customHeight="1">
       <x:c r="A190" s="7" t="n">
-        <x:v>1905</x:v>
+        <x:v>1906</x:v>
       </x:c>
       <x:c r="B190" s="7" t="n">
         <x:v>19</x:v>
       </x:c>
       <x:c r="C190" s="7" t="n">
-        <x:v>9</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D190" s="2" t="str">
-        <x:v>crate</x:v>
+        <x:v>plant</x:v>
       </x:c>
       <x:c r="E190" s="7" t="n">
-        <x:v>198</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="F190" s="7" t="n">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="191" ht="15" hidden="0" customHeight="1">
       <x:c r="A191" s="7" t="n">
-        <x:v>1906</x:v>
+        <x:v>1907</x:v>
       </x:c>
       <x:c r="B191" s="7" t="n">
         <x:v>19</x:v>
       </x:c>
       <x:c r="C191" s="7" t="n">
-        <x:v>11</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D191" s="2" t="str">
-        <x:v>plant</x:v>
+        <x:v>basket</x:v>
       </x:c>
       <x:c r="E191" s="7" t="n">
-        <x:v>203</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="F191" s="7" t="n">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="192" ht="15" hidden="0" customHeight="1">
       <x:c r="A192" s="7" t="n">
-        <x:v>1907</x:v>
+        <x:v>1908</x:v>
       </x:c>
       <x:c r="B192" s="7" t="n">
         <x:v>19</x:v>
       </x:c>
       <x:c r="C192" s="7" t="n">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D192" s="2" t="str">
-        <x:v>basket</x:v>
+        <x:v>crate</x:v>
       </x:c>
       <x:c r="E192" s="7" t="n">
-        <x:v>208</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="F192" s="7" t="n">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="193" ht="15" hidden="0" customHeight="1">
       <x:c r="A193" s="7" t="n">
-        <x:v>1908</x:v>
+        <x:v>1909</x:v>
       </x:c>
       <x:c r="B193" s="7" t="n">
         <x:v>19</x:v>
       </x:c>
       <x:c r="C193" s="7" t="n">
-        <x:v>15</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D193" s="2" t="str">
-        <x:v>crate</x:v>
+        <x:v>plant</x:v>
       </x:c>
       <x:c r="E193" s="7" t="n">
-        <x:v>213</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="F193" s="7" t="n">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="194" ht="15" hidden="0" customHeight="1">
       <x:c r="A194" s="7" t="n">
-        <x:v>1909</x:v>
+        <x:v>1910</x:v>
       </x:c>
       <x:c r="B194" s="7" t="n">
         <x:v>19</x:v>
       </x:c>
       <x:c r="C194" s="7" t="n">
-        <x:v>18</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D194" s="2" t="str">
-        <x:v>plant</x:v>
+        <x:v>basket</x:v>
       </x:c>
       <x:c r="E194" s="7" t="n">
-        <x:v>218</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="F194" s="7" t="n">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="195" ht="15" hidden="0" customHeight="1">
       <x:c r="A195" s="7" t="n">
-        <x:v>1910</x:v>
+        <x:v>2001</x:v>
       </x:c>
       <x:c r="B195" s="7" t="n">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C195" s="7" t="n">
-        <x:v>20</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D195" s="2" t="str">
         <x:v>basket</x:v>
       </x:c>
       <x:c r="E195" s="7" t="n">
-        <x:v>223</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="F195" s="7" t="n">
-        <x:v>57</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="196" ht="15" hidden="0" customHeight="1">
       <x:c r="A196" s="7" t="n">
-        <x:v>2001</x:v>
+        <x:v>2002</x:v>
       </x:c>
       <x:c r="B196" s="7" t="n">
         <x:v>20</x:v>
       </x:c>
       <x:c r="C196" s="7" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D196" s="2" t="str">
-        <x:v>basket</x:v>
+        <x:v>crate</x:v>
       </x:c>
       <x:c r="E196" s="7" t="n">
-        <x:v>184</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="F196" s="7" t="n">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="197" ht="15" hidden="0" customHeight="1">
       <x:c r="A197" s="7" t="n">
-        <x:v>2002</x:v>
+        <x:v>2003</x:v>
       </x:c>
       <x:c r="B197" s="7" t="n">
         <x:v>20</x:v>
       </x:c>
       <x:c r="C197" s="7" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D197" s="2" t="str">
-        <x:v>crate</x:v>
+        <x:v>plant</x:v>
       </x:c>
       <x:c r="E197" s="7" t="n">
-        <x:v>189</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="F197" s="7" t="n">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="198" ht="15" hidden="0" customHeight="1">
       <x:c r="A198" s="7" t="n">
-        <x:v>2003</x:v>
+        <x:v>2004</x:v>
       </x:c>
       <x:c r="B198" s="7" t="n">
         <x:v>20</x:v>
       </x:c>
       <x:c r="C198" s="7" t="n">
-        <x:v>5</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D198" s="2" t="str">
-        <x:v>plant</x:v>
+        <x:v>basket</x:v>
       </x:c>
       <x:c r="E198" s="7" t="n">
-        <x:v>194</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="F198" s="7" t="n">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="199" ht="15" hidden="0" customHeight="1">
       <x:c r="A199" s="7" t="n">
-        <x:v>2004</x:v>
+        <x:v>2005</x:v>
       </x:c>
       <x:c r="B199" s="7" t="n">
         <x:v>20</x:v>
       </x:c>
       <x:c r="C199" s="7" t="n">
-        <x:v>7</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D199" s="2" t="str">
-        <x:v>basket</x:v>
+        <x:v>crate</x:v>
       </x:c>
       <x:c r="E199" s="7" t="n">
-        <x:v>199</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="F199" s="7" t="n">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="200" ht="15" hidden="0" customHeight="1">
       <x:c r="A200" s="7" t="n">
-        <x:v>2005</x:v>
+        <x:v>2006</x:v>
       </x:c>
       <x:c r="B200" s="7" t="n">
         <x:v>20</x:v>
       </x:c>
       <x:c r="C200" s="7" t="n">
-        <x:v>9</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D200" s="2" t="str">
-        <x:v>crate</x:v>
+        <x:v>plant</x:v>
       </x:c>
       <x:c r="E200" s="7" t="n">
-        <x:v>204</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="F200" s="7" t="n">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="201" ht="15" hidden="0" customHeight="1">
       <x:c r="A201" s="7" t="n">
-        <x:v>2006</x:v>
+        <x:v>2007</x:v>
       </x:c>
       <x:c r="B201" s="7" t="n">
         <x:v>20</x:v>
       </x:c>
       <x:c r="C201" s="7" t="n">
-        <x:v>11</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D201" s="2" t="str">
-        <x:v>plant</x:v>
+        <x:v>basket</x:v>
       </x:c>
       <x:c r="E201" s="7" t="n">
-        <x:v>209</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="F201" s="7" t="n">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="202" ht="15" hidden="0" customHeight="1">
       <x:c r="A202" s="7" t="n">
-        <x:v>2007</x:v>
+        <x:v>2008</x:v>
       </x:c>
       <x:c r="B202" s="7" t="n">
         <x:v>20</x:v>
       </x:c>
       <x:c r="C202" s="7" t="n">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D202" s="2" t="str">
-        <x:v>basket</x:v>
+        <x:v>crate</x:v>
       </x:c>
       <x:c r="E202" s="7" t="n">
-        <x:v>214</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="F202" s="7" t="n">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="203" ht="15" hidden="0" customHeight="1">
       <x:c r="A203" s="7" t="n">
-        <x:v>2008</x:v>
+        <x:v>2009</x:v>
       </x:c>
       <x:c r="B203" s="7" t="n">
         <x:v>20</x:v>
       </x:c>
       <x:c r="C203" s="7" t="n">
-        <x:v>15</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D203" s="2" t="str">
-        <x:v>crate</x:v>
+        <x:v>plant</x:v>
       </x:c>
       <x:c r="E203" s="7" t="n">
-        <x:v>219</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="F203" s="7" t="n">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="204" ht="15" hidden="0" customHeight="1">
       <x:c r="A204" s="7" t="n">
-        <x:v>2009</x:v>
+        <x:v>2010</x:v>
       </x:c>
       <x:c r="B204" s="7" t="n">
         <x:v>20</x:v>
       </x:c>
       <x:c r="C204" s="7" t="n">
-        <x:v>18</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D204" s="2" t="str">
-        <x:v>plant</x:v>
+        <x:v>basket</x:v>
       </x:c>
       <x:c r="E204" s="7" t="n">
-        <x:v>224</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="F204" s="7" t="n">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="205" ht="15" hidden="0" customHeight="1">
       <x:c r="A205" s="7" t="n">
-        <x:v>2010</x:v>
+        <x:v>2011</x:v>
       </x:c>
       <x:c r="B205" s="7" t="n">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C205" s="7" t="n">
-        <x:v>20</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D205" s="2" t="str">
-        <x:v>basket</x:v>
+        <x:v>plant</x:v>
       </x:c>
       <x:c r="E205" s="7" t="n">
-        <x:v>229</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="F205" s="7" t="n">
-        <x:v>57</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="206">
       <x:c r="A206" t="n">
-        <x:v>2011</x:v>
+        <x:v>2012</x:v>
       </x:c>
       <x:c r="B206" t="n">
         <x:v>21</x:v>
       </x:c>
       <x:c r="C206" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D206" t="str">
-        <x:v>plant</x:v>
+        <x:v>crate</x:v>
       </x:c>
       <x:c r="E206" t="n">
-        <x:v>166</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="F206" t="n">
-        <x:v>48</x:v>
+        <x:v>62</x:v>
       </x:c>
     </x:row>
     <x:row r="207">
       <x:c r="A207" t="n">
-        <x:v>2012</x:v>
+        <x:v>2013</x:v>
       </x:c>
       <x:c r="B207" t="n">
         <x:v>21</x:v>
       </x:c>
       <x:c r="C207" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D207" t="str">
-        <x:v>crate</x:v>
+        <x:v>basket</x:v>
       </x:c>
       <x:c r="E207" t="n">
-        <x:v>212</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="F207" t="n">
-        <x:v>62</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="208">
       <x:c r="A208" t="n">
-        <x:v>2013</x:v>
+        <x:v>2014</x:v>
       </x:c>
       <x:c r="B208" t="n">
         <x:v>21</x:v>
       </x:c>
       <x:c r="C208" t="n">
-        <x:v>5</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D208" t="str">
-        <x:v>basket</x:v>
+        <x:v>crate</x:v>
       </x:c>
       <x:c r="E208" t="n">
-        <x:v>156</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="F208" t="n">
-        <x:v>46</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="209">
       <x:c r="A209" t="n">
-        <x:v>2014</x:v>
+        <x:v>2015</x:v>
       </x:c>
       <x:c r="B209" t="n">
         <x:v>21</x:v>
       </x:c>
       <x:c r="C209" t="n">
-        <x:v>7</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D209" t="str">
-        <x:v>crate</x:v>
+        <x:v>plant</x:v>
       </x:c>
       <x:c r="E209" t="n">
-        <x:v>226</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="F209" t="n">
-        <x:v>68</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="210">
       <x:c r="A210" t="n">
-        <x:v>2015</x:v>
+        <x:v>2016</x:v>
       </x:c>
       <x:c r="B210" t="n">
         <x:v>21</x:v>
       </x:c>
       <x:c r="C210" t="n">
-        <x:v>11</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D210" t="str">
-        <x:v>plant</x:v>
+        <x:v>basket</x:v>
       </x:c>
       <x:c r="E210" t="n">
-        <x:v>176</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="F210" t="n">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="211">
       <x:c r="A211" t="n">
-        <x:v>2016</x:v>
+        <x:v>2017</x:v>
       </x:c>
       <x:c r="B211" t="n">
         <x:v>21</x:v>
       </x:c>
       <x:c r="C211" t="n">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D211" t="str">
-        <x:v>basket</x:v>
+        <x:v>crate</x:v>
       </x:c>
       <x:c r="E211" t="n">
-        <x:v>166</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="F211" t="n">
-        <x:v>50</x:v>
+        <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="212">
       <x:c r="A212" t="n">
-        <x:v>2017</x:v>
+        <x:v>2018</x:v>
       </x:c>
       <x:c r="B212" t="n">
         <x:v>21</x:v>
       </x:c>
       <x:c r="C212" t="n">
-        <x:v>15</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D212" t="str">
-        <x:v>crate</x:v>
+        <x:v>plant</x:v>
       </x:c>
       <x:c r="E212" t="n">
-        <x:v>236</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="F212" t="n">
-        <x:v>70</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="213">
       <x:c r="A213" t="n">
-        <x:v>2018</x:v>
+        <x:v>2019</x:v>
       </x:c>
       <x:c r="B213" t="n">
         <x:v>21</x:v>
       </x:c>
       <x:c r="C213" t="n">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D213" t="str">
-        <x:v>plant</x:v>
+        <x:v>basket</x:v>
       </x:c>
       <x:c r="E213" t="n">
-        <x:v>184</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="F213" t="n">
         <x:v>54</x:v>
@@ -4550,43 +4550,31 @@
     </x:row>
     <x:row r="214">
       <x:c r="A214" t="n">
-        <x:v>2019</x:v>
+        <x:v>2020</x:v>
       </x:c>
       <x:c r="B214" t="n">
         <x:v>21</x:v>
       </x:c>
       <x:c r="C214" t="n">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D214" t="str">
-        <x:v>basket</x:v>
+        <x:v>crate</x:v>
       </x:c>
       <x:c r="E214" t="n">
-        <x:v>176</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="F214" t="n">
-        <x:v>54</x:v>
+        <x:v>74</x:v>
       </x:c>
     </x:row>
     <x:row r="215">
-      <x:c r="A215" t="n">
-        <x:v>2020</x:v>
-      </x:c>
-      <x:c r="B215" t="n">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C215" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D215" t="str">
-        <x:v>crate</x:v>
-      </x:c>
-      <x:c r="E215" t="n">
-        <x:v>248</x:v>
-      </x:c>
-      <x:c r="F215" t="n">
-        <x:v>74</x:v>
-      </x:c>
+      <x:c r="A215"/>
+      <x:c r="B215"/>
+      <x:c r="C215"/>
+      <x:c r="D215"/>
+      <x:c r="E215"/>
+      <x:c r="F215"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/design/tables/Obstacle.xlsx
+++ b/design/tables/Obstacle.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Obstacle" sheetId="1" r:id="Rb4e0de51a8e6494e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Obstacle" sheetId="1" r:id="Ra276ef471fd44230"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -3136,7 +3136,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C143" s="7" t="n">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D143" s="2" t="str">
         <x:v>crate</x:v>
@@ -3156,7 +3156,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C144" s="7" t="n">
-        <x:v>18</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D144" s="2" t="str">
         <x:v>plant</x:v>
@@ -3176,7 +3176,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C145" s="7" t="n">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D145" s="2" t="str">
         <x:v>basket</x:v>

--- a/design/tables/Obstacle.xlsx
+++ b/design/tables/Obstacle.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Obstacle" sheetId="1" r:id="Rf75724c9ef24486e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Obstacle" sheetId="1" r:id="R79ed8eb8ab40479e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -4607,12 +4607,2004 @@
       </x:c>
     </x:row>
     <x:row r="215">
-      <x:c r="A215"/>
-      <x:c r="B215"/>
-      <x:c r="C215"/>
-      <x:c r="D215"/>
-      <x:c r="E215"/>
-      <x:c r="F215"/>
+      <x:c r="A215" t="n">
+        <x:v>2201</x:v>
+      </x:c>
+      <x:c r="B215" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C215" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D215" t="str">
+        <x:v>basket</x:v>
+      </x:c>
+      <x:c r="E215" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F215" t="n">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="216">
+      <x:c r="A216" s="14" t="n">
+        <x:v>2202</x:v>
+      </x:c>
+      <x:c r="B216" s="14" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C216" s="14" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D216" s="15" t="str">
+        <x:v>crate</x:v>
+      </x:c>
+      <x:c r="E216" s="14" t="n">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="F216" s="14" t="n">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="217">
+      <x:c r="A217" s="14" t="n">
+        <x:v>2203</x:v>
+      </x:c>
+      <x:c r="B217" s="14" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C217" s="14" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D217" s="15" t="str">
+        <x:v>plant</x:v>
+      </x:c>
+      <x:c r="E217" s="14" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="F217" s="14" t="n">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="218">
+      <x:c r="A218" s="14" t="n">
+        <x:v>2204</x:v>
+      </x:c>
+      <x:c r="B218" s="14" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C218" s="14" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D218" s="15" t="str">
+        <x:v>basket</x:v>
+      </x:c>
+      <x:c r="E218" s="14" t="n">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="F218" s="14" t="n">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="219">
+      <x:c r="A219" s="14" t="n">
+        <x:v>2205</x:v>
+      </x:c>
+      <x:c r="B219" s="14" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C219" s="14" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D219" s="15" t="str">
+        <x:v>crate</x:v>
+      </x:c>
+      <x:c r="E219" s="14" t="n">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="F219" s="14" t="n">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="220">
+      <x:c r="A220" s="14" t="n">
+        <x:v>2206</x:v>
+      </x:c>
+      <x:c r="B220" s="14" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C220" s="14" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D220" s="15" t="str">
+        <x:v>plant</x:v>
+      </x:c>
+      <x:c r="E220" s="14" t="n">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="F220" s="14" t="n">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="221">
+      <x:c r="A221" s="14" t="n">
+        <x:v>2207</x:v>
+      </x:c>
+      <x:c r="B221" s="14" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C221" s="14" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D221" s="15" t="str">
+        <x:v>crate</x:v>
+      </x:c>
+      <x:c r="E221" s="14" t="n">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="F221" s="14" t="n">
+        <x:v>28</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="222">
+      <x:c r="A222" s="14" t="n">
+        <x:v>2208</x:v>
+      </x:c>
+      <x:c r="B222" s="14" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C222" s="14" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="D222" s="15" t="str">
+        <x:v>basket</x:v>
+      </x:c>
+      <x:c r="E222" s="14" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="F222" s="14" t="n">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="223">
+      <x:c r="A223" s="14" t="n">
+        <x:v>2209</x:v>
+      </x:c>
+      <x:c r="B223" s="14" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C223" s="14" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D223" s="15" t="str">
+        <x:v>plant</x:v>
+      </x:c>
+      <x:c r="E223" s="14" t="n">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="F223" s="14" t="n">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="224">
+      <x:c r="A224" s="14" t="n">
+        <x:v>2210</x:v>
+      </x:c>
+      <x:c r="B224" s="14" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C224" s="14" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D224" s="15" t="str">
+        <x:v>crate</x:v>
+      </x:c>
+      <x:c r="E224" s="14" t="n">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="F224" s="14" t="n">
+        <x:v>28</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="225">
+      <x:c r="A225" s="14" t="n">
+        <x:v>2301</x:v>
+      </x:c>
+      <x:c r="B225" s="14" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C225" s="14" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D225" s="15" t="str">
+        <x:v>plant</x:v>
+      </x:c>
+      <x:c r="E225" s="14" t="n">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="F225" s="14" t="n">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="226">
+      <x:c r="A226" s="14" t="n">
+        <x:v>2302</x:v>
+      </x:c>
+      <x:c r="B226" s="14" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C226" s="14" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D226" s="15" t="str">
+        <x:v>crate</x:v>
+      </x:c>
+      <x:c r="E226" s="14" t="n">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="F226" s="14" t="n">
+        <x:v>30</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="227">
+      <x:c r="A227" s="14" t="n">
+        <x:v>2303</x:v>
+      </x:c>
+      <x:c r="B227" s="14" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C227" s="14" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D227" s="15" t="str">
+        <x:v>basket</x:v>
+      </x:c>
+      <x:c r="E227" s="14" t="n">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="F227" s="14" t="n">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="228">
+      <x:c r="A228" s="14" t="n">
+        <x:v>2304</x:v>
+      </x:c>
+      <x:c r="B228" s="14" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C228" s="14" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D228" s="15" t="str">
+        <x:v>crate</x:v>
+      </x:c>
+      <x:c r="E228" s="14" t="n">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="F228" s="14" t="n">
+        <x:v>34</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="229">
+      <x:c r="A229" s="14" t="n">
+        <x:v>2305</x:v>
+      </x:c>
+      <x:c r="B229" s="14" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C229" s="14" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D229" s="15" t="str">
+        <x:v>plant</x:v>
+      </x:c>
+      <x:c r="E229" s="14" t="n">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="F229" s="14" t="n">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="230">
+      <x:c r="A230" s="14" t="n">
+        <x:v>2306</x:v>
+      </x:c>
+      <x:c r="B230" s="14" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C230" s="14" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D230" s="15" t="str">
+        <x:v>basket</x:v>
+      </x:c>
+      <x:c r="E230" s="14" t="n">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="F230" s="14" t="n">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="231">
+      <x:c r="A231" s="14" t="n">
+        <x:v>2307</x:v>
+      </x:c>
+      <x:c r="B231" s="14" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C231" s="14" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D231" s="15" t="str">
+        <x:v>crate</x:v>
+      </x:c>
+      <x:c r="E231" s="14" t="n">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="F231" s="14" t="n">
+        <x:v>38</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="232">
+      <x:c r="A232" s="14" t="n">
+        <x:v>2308</x:v>
+      </x:c>
+      <x:c r="B232" s="14" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C232" s="14" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D232" s="15" t="str">
+        <x:v>plant</x:v>
+      </x:c>
+      <x:c r="E232" s="14" t="n">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="F232" s="14" t="n">
+        <x:v>28</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="233">
+      <x:c r="A233" s="14" t="n">
+        <x:v>2309</x:v>
+      </x:c>
+      <x:c r="B233" s="14" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C233" s="14" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="D233" s="15" t="str">
+        <x:v>basket</x:v>
+      </x:c>
+      <x:c r="E233" s="14" t="n">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="F233" s="14" t="n">
+        <x:v>30</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="234">
+      <x:c r="A234" s="14" t="n">
+        <x:v>2310</x:v>
+      </x:c>
+      <x:c r="B234" s="14" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C234" s="14" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D234" s="15" t="str">
+        <x:v>crate</x:v>
+      </x:c>
+      <x:c r="E234" s="14" t="n">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="F234" s="14" t="n">
+        <x:v>38</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="235">
+      <x:c r="A235" s="14" t="n">
+        <x:v>2401</x:v>
+      </x:c>
+      <x:c r="B235" s="14" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C235" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D235" s="15" t="str">
+        <x:v>crate</x:v>
+      </x:c>
+      <x:c r="E235" s="14" t="n">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="F235" s="14" t="n">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="236">
+      <x:c r="A236" s="14" t="n">
+        <x:v>2402</x:v>
+      </x:c>
+      <x:c r="B236" s="14" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C236" s="14" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D236" s="15" t="str">
+        <x:v>basket</x:v>
+      </x:c>
+      <x:c r="E236" s="14" t="n">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="F236" s="14" t="n">
+        <x:v>28</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="237">
+      <x:c r="A237" s="14" t="n">
+        <x:v>2403</x:v>
+      </x:c>
+      <x:c r="B237" s="14" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C237" s="14" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D237" s="15" t="str">
+        <x:v>plant</x:v>
+      </x:c>
+      <x:c r="E237" s="14" t="n">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="F237" s="14" t="n">
+        <x:v>30</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="238">
+      <x:c r="A238" s="14" t="n">
+        <x:v>2404</x:v>
+      </x:c>
+      <x:c r="B238" s="14" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C238" s="14" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D238" s="15" t="str">
+        <x:v>crate</x:v>
+      </x:c>
+      <x:c r="E238" s="14" t="n">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="F238" s="14" t="n">
+        <x:v>40</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="239">
+      <x:c r="A239" s="14" t="n">
+        <x:v>2405</x:v>
+      </x:c>
+      <x:c r="B239" s="14" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C239" s="14" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D239" s="15" t="str">
+        <x:v>basket</x:v>
+      </x:c>
+      <x:c r="E239" s="14" t="n">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="F239" s="14" t="n">
+        <x:v>30</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="240">
+      <x:c r="A240" s="14" t="n">
+        <x:v>2406</x:v>
+      </x:c>
+      <x:c r="B240" s="14" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C240" s="14" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D240" s="15" t="str">
+        <x:v>plant</x:v>
+      </x:c>
+      <x:c r="E240" s="14" t="n">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="F240" s="14" t="n">
+        <x:v>34</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="241">
+      <x:c r="A241" s="14" t="n">
+        <x:v>2407</x:v>
+      </x:c>
+      <x:c r="B241" s="14" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C241" s="14" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="D241" s="15" t="str">
+        <x:v>crate</x:v>
+      </x:c>
+      <x:c r="E241" s="14" t="n">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="F241" s="14" t="n">
+        <x:v>44</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="242">
+      <x:c r="A242" s="14" t="n">
+        <x:v>2408</x:v>
+      </x:c>
+      <x:c r="B242" s="14" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C242" s="14" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D242" s="15" t="str">
+        <x:v>basket</x:v>
+      </x:c>
+      <x:c r="E242" s="14" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="F242" s="14" t="n">
+        <x:v>34</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="243">
+      <x:c r="A243" s="14" t="n">
+        <x:v>2409</x:v>
+      </x:c>
+      <x:c r="B243" s="14" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C243" s="14" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D243" s="15" t="str">
+        <x:v>plant</x:v>
+      </x:c>
+      <x:c r="E243" s="14" t="n">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="F243" s="14" t="n">
+        <x:v>36</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="244">
+      <x:c r="A244" s="14" t="n">
+        <x:v>2410</x:v>
+      </x:c>
+      <x:c r="B244" s="14" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C244" s="14" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D244" s="15" t="str">
+        <x:v>crate</x:v>
+      </x:c>
+      <x:c r="E244" s="14" t="n">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="F244" s="14" t="n">
+        <x:v>46</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="245">
+      <x:c r="A245" s="14" t="n">
+        <x:v>2501</x:v>
+      </x:c>
+      <x:c r="B245" s="14" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C245" s="14" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D245" s="15" t="str">
+        <x:v>basket</x:v>
+      </x:c>
+      <x:c r="E245" s="14" t="n">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="F245" s="14" t="n">
+        <x:v>36</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="246">
+      <x:c r="A246" s="14" t="n">
+        <x:v>2502</x:v>
+      </x:c>
+      <x:c r="B246" s="14" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C246" s="14" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D246" s="15" t="str">
+        <x:v>plant</x:v>
+      </x:c>
+      <x:c r="E246" s="14" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="F246" s="14" t="n">
+        <x:v>40</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="247">
+      <x:c r="A247" s="14" t="n">
+        <x:v>2503</x:v>
+      </x:c>
+      <x:c r="B247" s="14" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C247" s="14" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D247" s="15" t="str">
+        <x:v>crate</x:v>
+      </x:c>
+      <x:c r="E247" s="14" t="n">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="F247" s="14" t="n">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="248">
+      <x:c r="A248" s="14" t="n">
+        <x:v>2504</x:v>
+      </x:c>
+      <x:c r="B248" s="14" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C248" s="14" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D248" s="15" t="str">
+        <x:v>basket</x:v>
+      </x:c>
+      <x:c r="E248" s="14" t="n">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="F248" s="14" t="n">
+        <x:v>40</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="249">
+      <x:c r="A249" s="14" t="n">
+        <x:v>2505</x:v>
+      </x:c>
+      <x:c r="B249" s="14" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C249" s="14" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="D249" s="15" t="str">
+        <x:v>crate</x:v>
+      </x:c>
+      <x:c r="E249" s="14" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="F249" s="14" t="n">
+        <x:v>56</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="250">
+      <x:c r="A250" s="14" t="n">
+        <x:v>2506</x:v>
+      </x:c>
+      <x:c r="B250" s="14" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C250" s="14" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D250" s="15" t="str">
+        <x:v>plant</x:v>
+      </x:c>
+      <x:c r="E250" s="14" t="n">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="F250" s="14" t="n">
+        <x:v>44</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="251">
+      <x:c r="A251" s="14" t="n">
+        <x:v>2507</x:v>
+      </x:c>
+      <x:c r="B251" s="14" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C251" s="14" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D251" s="15" t="str">
+        <x:v>basket</x:v>
+      </x:c>
+      <x:c r="E251" s="14" t="n">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="F251" s="14" t="n">
+        <x:v>44</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="252">
+      <x:c r="A252" s="14" t="n">
+        <x:v>2508</x:v>
+      </x:c>
+      <x:c r="B252" s="14" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C252" s="14" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D252" s="15" t="str">
+        <x:v>crate</x:v>
+      </x:c>
+      <x:c r="E252" s="14" t="n">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="F252" s="14" t="n">
+        <x:v>58</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="253">
+      <x:c r="A253" s="14" t="n">
+        <x:v>2509</x:v>
+      </x:c>
+      <x:c r="B253" s="14" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C253" s="14" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D253" s="15" t="str">
+        <x:v>plant</x:v>
+      </x:c>
+      <x:c r="E253" s="14" t="n">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="F253" s="14" t="n">
+        <x:v>46</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="254">
+      <x:c r="A254" s="14" t="n">
+        <x:v>2510</x:v>
+      </x:c>
+      <x:c r="B254" s="14" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C254" s="14" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D254" s="15" t="str">
+        <x:v>crate</x:v>
+      </x:c>
+      <x:c r="E254" s="14" t="n">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="F254" s="14" t="n">
+        <x:v>60</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="255">
+      <x:c r="A255" s="14" t="n">
+        <x:v>2601</x:v>
+      </x:c>
+      <x:c r="B255" s="14" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C255" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D255" s="15" t="str">
+        <x:v>plant</x:v>
+      </x:c>
+      <x:c r="E255" s="14" t="n">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="F255" s="14" t="n">
+        <x:v>48</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="256">
+      <x:c r="A256" s="14" t="n">
+        <x:v>2602</x:v>
+      </x:c>
+      <x:c r="B256" s="14" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C256" s="14" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D256" s="15" t="str">
+        <x:v>crate</x:v>
+      </x:c>
+      <x:c r="E256" s="14" t="n">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="F256" s="14" t="n">
+        <x:v>62</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="257">
+      <x:c r="A257" s="14" t="n">
+        <x:v>2603</x:v>
+      </x:c>
+      <x:c r="B257" s="14" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C257" s="14" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D257" s="15" t="str">
+        <x:v>basket</x:v>
+      </x:c>
+      <x:c r="E257" s="14" t="n">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="F257" s="14" t="n">
+        <x:v>46</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="258">
+      <x:c r="A258" s="14" t="n">
+        <x:v>2604</x:v>
+      </x:c>
+      <x:c r="B258" s="14" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C258" s="14" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D258" s="15" t="str">
+        <x:v>crate</x:v>
+      </x:c>
+      <x:c r="E258" s="14" t="n">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="F258" s="14" t="n">
+        <x:v>74</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="259">
+      <x:c r="A259" s="14" t="n">
+        <x:v>2605</x:v>
+      </x:c>
+      <x:c r="B259" s="14" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C259" s="14" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="D259" s="15" t="str">
+        <x:v>plant</x:v>
+      </x:c>
+      <x:c r="E259" s="14" t="n">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="F259" s="14" t="n">
+        <x:v>52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="260">
+      <x:c r="A260" s="14" t="n">
+        <x:v>2606</x:v>
+      </x:c>
+      <x:c r="B260" s="14" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C260" s="14" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D260" s="15" t="str">
+        <x:v>basket</x:v>
+      </x:c>
+      <x:c r="E260" s="14" t="n">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="F260" s="14" t="n">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="261">
+      <x:c r="A261" s="14" t="n">
+        <x:v>2607</x:v>
+      </x:c>
+      <x:c r="B261" s="14" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C261" s="14" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D261" s="15" t="str">
+        <x:v>crate</x:v>
+      </x:c>
+      <x:c r="E261" s="14" t="n">
+        <x:v>236</x:v>
+      </x:c>
+      <x:c r="F261" s="14" t="n">
+        <x:v>70</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="262">
+      <x:c r="A262" s="14" t="n">
+        <x:v>2608</x:v>
+      </x:c>
+      <x:c r="B262" s="14" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C262" s="14" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D262" s="15" t="str">
+        <x:v>plant</x:v>
+      </x:c>
+      <x:c r="E262" s="14" t="n">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="F262" s="14" t="n">
+        <x:v>54</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="263">
+      <x:c r="A263" s="14" t="n">
+        <x:v>2609</x:v>
+      </x:c>
+      <x:c r="B263" s="14" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C263" s="14" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="D263" s="15" t="str">
+        <x:v>basket</x:v>
+      </x:c>
+      <x:c r="E263" s="14" t="n">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="F263" s="14" t="n">
+        <x:v>54</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="264">
+      <x:c r="A264" s="14" t="n">
+        <x:v>2610</x:v>
+      </x:c>
+      <x:c r="B264" s="14" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C264" s="14" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D264" s="15" t="str">
+        <x:v>crate</x:v>
+      </x:c>
+      <x:c r="E264" s="14" t="n">
+        <x:v>248</x:v>
+      </x:c>
+      <x:c r="F264" s="14" t="n">
+        <x:v>74</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="265">
+      <x:c r="A265" s="14" t="n">
+        <x:v>2701</x:v>
+      </x:c>
+      <x:c r="B265" s="14" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C265" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D265" s="15" t="str">
+        <x:v>basket</x:v>
+      </x:c>
+      <x:c r="E265" s="14" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="F265" s="14" t="n">
+        <x:v>40</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="266">
+      <x:c r="A266" s="14" t="n">
+        <x:v>2702</x:v>
+      </x:c>
+      <x:c r="B266" s="14" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C266" s="14" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D266" s="15" t="str">
+        <x:v>crate</x:v>
+      </x:c>
+      <x:c r="E266" s="14" t="n">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="F266" s="14" t="n">
+        <x:v>41</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="267">
+      <x:c r="A267" s="14" t="n">
+        <x:v>2703</x:v>
+      </x:c>
+      <x:c r="B267" s="14" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C267" s="14" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D267" s="15" t="str">
+        <x:v>plant</x:v>
+      </x:c>
+      <x:c r="E267" s="14" t="n">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="F267" s="14" t="n">
+        <x:v>42</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="268">
+      <x:c r="A268" s="14" t="n">
+        <x:v>2704</x:v>
+      </x:c>
+      <x:c r="B268" s="14" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C268" s="14" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D268" s="15" t="str">
+        <x:v>basket</x:v>
+      </x:c>
+      <x:c r="E268" s="14" t="n">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="F268" s="14" t="n">
+        <x:v>43</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="269">
+      <x:c r="A269" s="14" t="n">
+        <x:v>2705</x:v>
+      </x:c>
+      <x:c r="B269" s="14" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C269" s="14" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D269" s="15" t="str">
+        <x:v>crate</x:v>
+      </x:c>
+      <x:c r="E269" s="14" t="n">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="F269" s="14" t="n">
+        <x:v>44</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="270">
+      <x:c r="A270" s="14" t="n">
+        <x:v>2706</x:v>
+      </x:c>
+      <x:c r="B270" s="14" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C270" s="14" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="D270" s="15" t="str">
+        <x:v>plant</x:v>
+      </x:c>
+      <x:c r="E270" s="14" t="n">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="F270" s="14" t="n">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="271">
+      <x:c r="A271" s="14" t="n">
+        <x:v>2707</x:v>
+      </x:c>
+      <x:c r="B271" s="14" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C271" s="14" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D271" s="15" t="str">
+        <x:v>basket</x:v>
+      </x:c>
+      <x:c r="E271" s="14" t="n">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="F271" s="14" t="n">
+        <x:v>46</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="272">
+      <x:c r="A272" s="14" t="n">
+        <x:v>2708</x:v>
+      </x:c>
+      <x:c r="B272" s="14" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C272" s="14" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D272" s="15" t="str">
+        <x:v>crate</x:v>
+      </x:c>
+      <x:c r="E272" s="14" t="n">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="F272" s="14" t="n">
+        <x:v>47</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="273">
+      <x:c r="A273" s="14" t="n">
+        <x:v>2709</x:v>
+      </x:c>
+      <x:c r="B273" s="14" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C273" s="14" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D273" s="15" t="str">
+        <x:v>plant</x:v>
+      </x:c>
+      <x:c r="E273" s="14" t="n">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="F273" s="14" t="n">
+        <x:v>48</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="274">
+      <x:c r="A274" s="14" t="n">
+        <x:v>2710</x:v>
+      </x:c>
+      <x:c r="B274" s="14" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C274" s="14" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D274" s="15" t="str">
+        <x:v>basket</x:v>
+      </x:c>
+      <x:c r="E274" s="14" t="n">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="F274" s="14" t="n">
+        <x:v>49</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="275">
+      <x:c r="A275" s="14" t="n">
+        <x:v>2801</x:v>
+      </x:c>
+      <x:c r="B275" s="14" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C275" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D275" s="15" t="str">
+        <x:v>basket</x:v>
+      </x:c>
+      <x:c r="E275" s="14" t="n">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="F275" s="14" t="n">
+        <x:v>40</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="276">
+      <x:c r="A276" s="14" t="n">
+        <x:v>2802</x:v>
+      </x:c>
+      <x:c r="B276" s="14" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C276" s="14" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D276" s="15" t="str">
+        <x:v>crate</x:v>
+      </x:c>
+      <x:c r="E276" s="14" t="n">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="F276" s="14" t="n">
+        <x:v>41</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="277">
+      <x:c r="A277" s="14" t="n">
+        <x:v>2803</x:v>
+      </x:c>
+      <x:c r="B277" s="14" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C277" s="14" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D277" s="15" t="str">
+        <x:v>plant</x:v>
+      </x:c>
+      <x:c r="E277" s="14" t="n">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="F277" s="14" t="n">
+        <x:v>42</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="278">
+      <x:c r="A278" s="14" t="n">
+        <x:v>2804</x:v>
+      </x:c>
+      <x:c r="B278" s="14" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C278" s="14" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D278" s="15" t="str">
+        <x:v>basket</x:v>
+      </x:c>
+      <x:c r="E278" s="14" t="n">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="F278" s="14" t="n">
+        <x:v>43</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="279">
+      <x:c r="A279" s="14" t="n">
+        <x:v>2805</x:v>
+      </x:c>
+      <x:c r="B279" s="14" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C279" s="14" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D279" s="15" t="str">
+        <x:v>crate</x:v>
+      </x:c>
+      <x:c r="E279" s="14" t="n">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="F279" s="14" t="n">
+        <x:v>44</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="280">
+      <x:c r="A280" s="14" t="n">
+        <x:v>2806</x:v>
+      </x:c>
+      <x:c r="B280" s="14" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C280" s="14" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="D280" s="15" t="str">
+        <x:v>plant</x:v>
+      </x:c>
+      <x:c r="E280" s="14" t="n">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="F280" s="14" t="n">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="281">
+      <x:c r="A281" s="14" t="n">
+        <x:v>2807</x:v>
+      </x:c>
+      <x:c r="B281" s="14" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C281" s="14" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D281" s="15" t="str">
+        <x:v>basket</x:v>
+      </x:c>
+      <x:c r="E281" s="14" t="n">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="F281" s="14" t="n">
+        <x:v>46</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="282">
+      <x:c r="A282" s="14" t="n">
+        <x:v>2808</x:v>
+      </x:c>
+      <x:c r="B282" s="14" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C282" s="14" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D282" s="15" t="str">
+        <x:v>crate</x:v>
+      </x:c>
+      <x:c r="E282" s="14" t="n">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="F282" s="14" t="n">
+        <x:v>47</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="283">
+      <x:c r="A283" s="14" t="n">
+        <x:v>2809</x:v>
+      </x:c>
+      <x:c r="B283" s="14" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C283" s="14" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D283" s="15" t="str">
+        <x:v>plant</x:v>
+      </x:c>
+      <x:c r="E283" s="14" t="n">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="F283" s="14" t="n">
+        <x:v>48</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="284">
+      <x:c r="A284" s="14" t="n">
+        <x:v>2810</x:v>
+      </x:c>
+      <x:c r="B284" s="14" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C284" s="14" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D284" s="15" t="str">
+        <x:v>basket</x:v>
+      </x:c>
+      <x:c r="E284" s="14" t="n">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="F284" s="14" t="n">
+        <x:v>49</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="285">
+      <x:c r="A285" s="14" t="n">
+        <x:v>2901</x:v>
+      </x:c>
+      <x:c r="B285" s="14" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C285" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D285" s="15" t="str">
+        <x:v>basket</x:v>
+      </x:c>
+      <x:c r="E285" s="14" t="n">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="F285" s="14" t="n">
+        <x:v>37</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="286">
+      <x:c r="A286" s="14" t="n">
+        <x:v>2902</x:v>
+      </x:c>
+      <x:c r="B286" s="14" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C286" s="14" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D286" s="15" t="str">
+        <x:v>crate</x:v>
+      </x:c>
+      <x:c r="E286" s="14" t="n">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="F286" s="14" t="n">
+        <x:v>75</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="287">
+      <x:c r="A287" s="14" t="n">
+        <x:v>2903</x:v>
+      </x:c>
+      <x:c r="B287" s="14" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C287" s="14" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D287" s="15" t="str">
+        <x:v>plant</x:v>
+      </x:c>
+      <x:c r="E287" s="14" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="F287" s="14" t="n">
+        <x:v>37</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="288">
+      <x:c r="A288" s="14" t="n">
+        <x:v>2904</x:v>
+      </x:c>
+      <x:c r="B288" s="14" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C288" s="14" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D288" s="15" t="str">
+        <x:v>basket</x:v>
+      </x:c>
+      <x:c r="E288" s="14" t="n">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="F288" s="14" t="n">
+        <x:v>37</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="289">
+      <x:c r="A289" s="14" t="n">
+        <x:v>2905</x:v>
+      </x:c>
+      <x:c r="B289" s="14" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C289" s="14" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D289" s="15" t="str">
+        <x:v>crate</x:v>
+      </x:c>
+      <x:c r="E289" s="14" t="n">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="F289" s="14" t="n">
+        <x:v>75</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="290">
+      <x:c r="A290" s="14" t="n">
+        <x:v>2906</x:v>
+      </x:c>
+      <x:c r="B290" s="14" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C290" s="14" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="D290" s="15" t="str">
+        <x:v>plant</x:v>
+      </x:c>
+      <x:c r="E290" s="14" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="F290" s="14" t="n">
+        <x:v>37</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="291">
+      <x:c r="A291" s="14" t="n">
+        <x:v>2907</x:v>
+      </x:c>
+      <x:c r="B291" s="14" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C291" s="14" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D291" s="15" t="str">
+        <x:v>basket</x:v>
+      </x:c>
+      <x:c r="E291" s="14" t="n">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="F291" s="14" t="n">
+        <x:v>37</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="292">
+      <x:c r="A292" s="14" t="n">
+        <x:v>2908</x:v>
+      </x:c>
+      <x:c r="B292" s="14" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C292" s="14" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D292" s="15" t="str">
+        <x:v>crate</x:v>
+      </x:c>
+      <x:c r="E292" s="14" t="n">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="F292" s="14" t="n">
+        <x:v>75</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="293">
+      <x:c r="A293" s="14" t="n">
+        <x:v>2909</x:v>
+      </x:c>
+      <x:c r="B293" s="14" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C293" s="14" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D293" s="15" t="str">
+        <x:v>plant</x:v>
+      </x:c>
+      <x:c r="E293" s="14" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="F293" s="14" t="n">
+        <x:v>37</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="294">
+      <x:c r="A294" s="14" t="n">
+        <x:v>2910</x:v>
+      </x:c>
+      <x:c r="B294" s="14" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C294" s="14" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D294" s="15" t="str">
+        <x:v>basket</x:v>
+      </x:c>
+      <x:c r="E294" s="14" t="n">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="F294" s="14" t="n">
+        <x:v>37</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="295">
+      <x:c r="A295" s="14" t="n">
+        <x:v>3001</x:v>
+      </x:c>
+      <x:c r="B295" s="14" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C295" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D295" s="15" t="str">
+        <x:v>basket</x:v>
+      </x:c>
+      <x:c r="E295" s="14" t="n">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="F295" s="14" t="n">
+        <x:v>48</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="296">
+      <x:c r="A296" s="14" t="n">
+        <x:v>3002</x:v>
+      </x:c>
+      <x:c r="B296" s="14" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C296" s="14" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D296" s="15" t="str">
+        <x:v>crate</x:v>
+      </x:c>
+      <x:c r="E296" s="14" t="n">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="F296" s="14" t="n">
+        <x:v>49</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="297">
+      <x:c r="A297" s="14" t="n">
+        <x:v>3003</x:v>
+      </x:c>
+      <x:c r="B297" s="14" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C297" s="14" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D297" s="15" t="str">
+        <x:v>plant</x:v>
+      </x:c>
+      <x:c r="E297" s="14" t="n">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="F297" s="14" t="n">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="298">
+      <x:c r="A298" s="14" t="n">
+        <x:v>3004</x:v>
+      </x:c>
+      <x:c r="B298" s="14" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C298" s="14" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D298" s="15" t="str">
+        <x:v>basket</x:v>
+      </x:c>
+      <x:c r="E298" s="14" t="n">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="F298" s="14" t="n">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="299">
+      <x:c r="A299" s="14" t="n">
+        <x:v>3005</x:v>
+      </x:c>
+      <x:c r="B299" s="14" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C299" s="14" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D299" s="15" t="str">
+        <x:v>crate</x:v>
+      </x:c>
+      <x:c r="E299" s="14" t="n">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="F299" s="14" t="n">
+        <x:v>52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="300">
+      <x:c r="A300" s="14" t="n">
+        <x:v>3006</x:v>
+      </x:c>
+      <x:c r="B300" s="14" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C300" s="14" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="D300" s="15" t="str">
+        <x:v>plant</x:v>
+      </x:c>
+      <x:c r="E300" s="14" t="n">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="F300" s="14" t="n">
+        <x:v>53</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="301">
+      <x:c r="A301" s="14" t="n">
+        <x:v>3007</x:v>
+      </x:c>
+      <x:c r="B301" s="14" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C301" s="14" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D301" s="15" t="str">
+        <x:v>basket</x:v>
+      </x:c>
+      <x:c r="E301" s="14" t="n">
+        <x:v>208</x:v>
+      </x:c>
+      <x:c r="F301" s="14" t="n">
+        <x:v>54</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="302">
+      <x:c r="A302" s="14" t="n">
+        <x:v>3008</x:v>
+      </x:c>
+      <x:c r="B302" s="14" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C302" s="14" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D302" s="15" t="str">
+        <x:v>crate</x:v>
+      </x:c>
+      <x:c r="E302" s="14" t="n">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="F302" s="14" t="n">
+        <x:v>55</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="303">
+      <x:c r="A303" s="14" t="n">
+        <x:v>3009</x:v>
+      </x:c>
+      <x:c r="B303" s="14" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C303" s="14" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D303" s="15" t="str">
+        <x:v>plant</x:v>
+      </x:c>
+      <x:c r="E303" s="14" t="n">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="F303" s="14" t="n">
+        <x:v>56</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="304">
+      <x:c r="A304" s="14" t="n">
+        <x:v>3010</x:v>
+      </x:c>
+      <x:c r="B304" s="14" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C304" s="14" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D304" s="15" t="str">
+        <x:v>basket</x:v>
+      </x:c>
+      <x:c r="E304" s="14" t="n">
+        <x:v>223</x:v>
+      </x:c>
+      <x:c r="F304" s="14" t="n">
+        <x:v>57</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="305">
+      <x:c r="A305" s="14" t="n">
+        <x:v>3101</x:v>
+      </x:c>
+      <x:c r="B305" s="14" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C305" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D305" s="15" t="str">
+        <x:v>basket</x:v>
+      </x:c>
+      <x:c r="E305" s="14" t="n">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="F305" s="14" t="n">
+        <x:v>48</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="306">
+      <x:c r="A306" s="14" t="n">
+        <x:v>3102</x:v>
+      </x:c>
+      <x:c r="B306" s="14" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C306" s="14" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D306" s="15" t="str">
+        <x:v>crate</x:v>
+      </x:c>
+      <x:c r="E306" s="14" t="n">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="F306" s="14" t="n">
+        <x:v>49</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="307">
+      <x:c r="A307" s="14" t="n">
+        <x:v>3103</x:v>
+      </x:c>
+      <x:c r="B307" s="14" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C307" s="14" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D307" s="15" t="str">
+        <x:v>plant</x:v>
+      </x:c>
+      <x:c r="E307" s="14" t="n">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="F307" s="14" t="n">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="308">
+      <x:c r="A308" s="14" t="n">
+        <x:v>3104</x:v>
+      </x:c>
+      <x:c r="B308" s="14" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C308" s="14" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D308" s="15" t="str">
+        <x:v>basket</x:v>
+      </x:c>
+      <x:c r="E308" s="14" t="n">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="F308" s="14" t="n">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="309">
+      <x:c r="A309" s="14" t="n">
+        <x:v>3105</x:v>
+      </x:c>
+      <x:c r="B309" s="14" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C309" s="14" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D309" s="15" t="str">
+        <x:v>crate</x:v>
+      </x:c>
+      <x:c r="E309" s="14" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="F309" s="14" t="n">
+        <x:v>60</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="310">
+      <x:c r="A310" s="14" t="n">
+        <x:v>3106</x:v>
+      </x:c>
+      <x:c r="B310" s="14" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C310" s="14" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="D310" s="15" t="str">
+        <x:v>plant</x:v>
+      </x:c>
+      <x:c r="E310" s="14" t="n">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="F310" s="14" t="n">
+        <x:v>53</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="311">
+      <x:c r="A311" s="14" t="n">
+        <x:v>3107</x:v>
+      </x:c>
+      <x:c r="B311" s="14" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C311" s="14" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D311" s="15" t="str">
+        <x:v>basket</x:v>
+      </x:c>
+      <x:c r="E311" s="14" t="n">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="F311" s="14" t="n">
+        <x:v>54</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="312">
+      <x:c r="A312" s="14" t="n">
+        <x:v>3108</x:v>
+      </x:c>
+      <x:c r="B312" s="14" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C312" s="14" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D312" s="15" t="str">
+        <x:v>crate</x:v>
+      </x:c>
+      <x:c r="E312" s="14" t="n">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="F312" s="14" t="n">
+        <x:v>55</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="313">
+      <x:c r="A313" s="14" t="n">
+        <x:v>3109</x:v>
+      </x:c>
+      <x:c r="B313" s="14" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C313" s="14" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D313" s="15" t="str">
+        <x:v>plant</x:v>
+      </x:c>
+      <x:c r="E313" s="14" t="n">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="F313" s="14" t="n">
+        <x:v>56</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="314">
+      <x:c r="A314" s="14" t="n">
+        <x:v>3110</x:v>
+      </x:c>
+      <x:c r="B314" s="14" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C314" s="14" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D314" s="15" t="str">
+        <x:v>basket</x:v>
+      </x:c>
+      <x:c r="E314" s="14" t="n">
+        <x:v>229</x:v>
+      </x:c>
+      <x:c r="F314" s="14" t="n">
+        <x:v>57</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
